--- a/output/yearly_benthic_cover_iteration_72_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_72_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.39336029122988</v>
+        <v>45.63786182817462</v>
       </c>
       <c r="M2" t="n">
-        <v>99.79848012284228</v>
+        <v>98.79358371536202</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.03870168195093</v>
+        <v>88.06808539073904</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93401484972972</v>
+        <v>45.9361494010403</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228755794127042</v>
+        <v>2.228829513010365</v>
       </c>
       <c r="E3" t="n">
-        <v>5.71001198086314</v>
+        <v>5.712882911122991</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429185980423472</v>
+        <v>0.7429431710034549</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97485602023942</v>
+        <v>33.97528002948486</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17425550994797</v>
+        <v>34.17538586615892</v>
       </c>
       <c r="I3" t="n">
-        <v>6.564662540966339</v>
+        <v>6.589369081186859</v>
       </c>
       <c r="J3" t="n">
-        <v>4.64324123776467</v>
+        <v>4.643394818771593</v>
       </c>
       <c r="K3" t="n">
-        <v>11.96129831804907</v>
+        <v>11.93191460926096</v>
       </c>
       <c r="L3" t="n">
-        <v>48.86905177311729</v>
+        <v>48.89542192551491</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7643649408961</v>
+        <v>106.7634859358162</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.02645555797848</v>
+        <v>87.29232983207825</v>
       </c>
       <c r="C4" t="n">
-        <v>42.55605495554484</v>
+        <v>42.79937021612571</v>
       </c>
       <c r="D4" t="n">
-        <v>2.179496463579258</v>
+        <v>2.192177327926861</v>
       </c>
       <c r="E4" t="n">
-        <v>6.497484070404351</v>
+        <v>6.536050089767441</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444785484710753</v>
+        <v>0.7445042771912533</v>
       </c>
       <c r="G4" t="n">
-        <v>33.22395335632965</v>
+        <v>33.41657051642631</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24601322966947</v>
+        <v>34.24719675079765</v>
       </c>
       <c r="I4" t="n">
-        <v>5.482038961580467</v>
+        <v>5.502679137523385</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652990927944221</v>
+        <v>4.653151732445333</v>
       </c>
       <c r="K4" t="n">
-        <v>12.97354444202151</v>
+        <v>12.70767016792176</v>
       </c>
       <c r="L4" t="n">
-        <v>44.28804886518459</v>
+        <v>44.30992158591956</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81764826275094</v>
+        <v>99.81696196996704</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.75005582464573</v>
+        <v>86.22427890934894</v>
       </c>
       <c r="C5" t="n">
-        <v>42.1304070056711</v>
+        <v>42.58551227990525</v>
       </c>
       <c r="D5" t="n">
-        <v>2.116863163019884</v>
+        <v>2.140416638858728</v>
       </c>
       <c r="E5" t="n">
-        <v>7.073511383882694</v>
+        <v>7.147342086769423</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458029794166965</v>
+        <v>0.7458264246185063</v>
       </c>
       <c r="G5" t="n">
-        <v>32.26917967758725</v>
+        <v>32.62755372741508</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30693705316804</v>
+        <v>34.30801553245129</v>
       </c>
       <c r="I5" t="n">
-        <v>4.576492946216808</v>
+        <v>4.593709345370264</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661268621354353</v>
+        <v>4.661415153865664</v>
       </c>
       <c r="K5" t="n">
-        <v>14.24994417535425</v>
+        <v>13.77572109065107</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46736995893075</v>
+        <v>43.48591443117913</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84772113995611</v>
+        <v>99.84714780173545</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.30569617972223</v>
+        <v>85.01219960608788</v>
       </c>
       <c r="C6" t="n">
-        <v>41.39662157929089</v>
+        <v>42.08707476125765</v>
       </c>
       <c r="D6" t="n">
-        <v>2.046201781803348</v>
+        <v>2.081646029093897</v>
       </c>
       <c r="E6" t="n">
-        <v>7.47397986750364</v>
+        <v>7.590067826234931</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469292762411437</v>
+        <v>0.7469475905423629</v>
       </c>
       <c r="G6" t="n">
-        <v>31.1920270082149</v>
+        <v>31.73168084319129</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35874670709261</v>
+        <v>34.35958916494869</v>
       </c>
       <c r="I6" t="n">
-        <v>3.819503562359431</v>
+        <v>3.833845711186933</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668307976507148</v>
+        <v>4.668422440889768</v>
       </c>
       <c r="K6" t="n">
-        <v>15.69430382027778</v>
+        <v>14.98780039391213</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78194979636974</v>
+        <v>42.79752180745884</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87287519593841</v>
+        <v>99.87239696262861</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.59385710342619</v>
+        <v>83.6182174459135</v>
       </c>
       <c r="C7" t="n">
-        <v>40.27778546335028</v>
+        <v>41.28883869988631</v>
       </c>
       <c r="D7" t="n">
-        <v>1.962685690945869</v>
+        <v>2.014125713430605</v>
       </c>
       <c r="E7" t="n">
-        <v>7.700096973339372</v>
+        <v>7.877033819573924</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478899908432468</v>
+        <v>0.7479001121222681</v>
       </c>
       <c r="G7" t="n">
-        <v>29.91891885983319</v>
+        <v>30.70243135643213</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40293957878936</v>
+        <v>34.40340515762433</v>
       </c>
       <c r="I7" t="n">
-        <v>3.18701356690486</v>
+        <v>3.198945585966074</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674312442770293</v>
+        <v>4.674375700764175</v>
       </c>
       <c r="K7" t="n">
-        <v>17.4061428965738</v>
+        <v>16.38178255408648</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20997431889929</v>
+        <v>42.22288303182757</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89390267882337</v>
+        <v>99.89350428580038</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.40939657526239</v>
+        <v>88.44743595402461</v>
       </c>
       <c r="C8" t="n">
-        <v>42.53198101241535</v>
+        <v>43.55131649670006</v>
       </c>
       <c r="D8" t="n">
-        <v>1.966895881903669</v>
+        <v>2.018408842781888</v>
       </c>
       <c r="E8" t="n">
-        <v>9.500529514334394</v>
+        <v>9.683613663319187</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494943025735473</v>
+        <v>0.7494905555095395</v>
       </c>
       <c r="G8" t="n">
-        <v>30.40629740030976</v>
+        <v>31.19241727777572</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47673791838318</v>
+        <v>34.47656555343881</v>
       </c>
       <c r="I8" t="n">
-        <v>5.625102166673162</v>
+        <v>5.642624089264838</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684339391084671</v>
+        <v>4.684315971934621</v>
       </c>
       <c r="K8" t="n">
-        <v>12.5906034247376</v>
+        <v>11.55256404597541</v>
       </c>
       <c r="L8" t="n">
-        <v>44.69031351312809</v>
+        <v>44.70843111542335</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81289795028106</v>
+        <v>99.81231165809882</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.24445261444858</v>
+        <v>86.56793994429653</v>
       </c>
       <c r="C9" t="n">
-        <v>41.23953732812326</v>
+        <v>42.54813211983392</v>
       </c>
       <c r="D9" t="n">
-        <v>1.86862915159149</v>
+        <v>1.933469408795101</v>
       </c>
       <c r="E9" t="n">
-        <v>9.808578978069802</v>
+        <v>10.06122354421283</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508706463218222</v>
+        <v>0.7508500415240487</v>
       </c>
       <c r="G9" t="n">
-        <v>28.88718932045742</v>
+        <v>29.87976633605556</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54004973080382</v>
+        <v>34.53910191010623</v>
       </c>
       <c r="I9" t="n">
-        <v>4.696193247692821</v>
+        <v>4.710715944077448</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69294153951139</v>
+        <v>4.692812759525304</v>
       </c>
       <c r="K9" t="n">
-        <v>14.75554738555143</v>
+        <v>13.43206005570349</v>
       </c>
       <c r="L9" t="n">
-        <v>43.84866244836215</v>
+        <v>43.86306826642746</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84374716203685</v>
+        <v>99.84326044196487</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.8434885739813</v>
+        <v>84.47729581325036</v>
       </c>
       <c r="C10" t="n">
-        <v>39.56655311815281</v>
+        <v>41.18893130288546</v>
       </c>
       <c r="D10" t="n">
-        <v>1.760799606320272</v>
+        <v>1.839787882796201</v>
       </c>
       <c r="E10" t="n">
-        <v>9.895851101459925</v>
+        <v>10.22901271025092</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520548723694072</v>
+        <v>0.7520148938065251</v>
       </c>
       <c r="G10" t="n">
-        <v>27.22024942179663</v>
+        <v>28.43201542046355</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59452412899273</v>
+        <v>34.59268511510015</v>
       </c>
       <c r="I10" t="n">
-        <v>3.919666490733538</v>
+        <v>3.931686704542237</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700342952308795</v>
+        <v>4.700093086290781</v>
       </c>
       <c r="K10" t="n">
-        <v>17.15651142601871</v>
+        <v>15.52270418674964</v>
       </c>
       <c r="L10" t="n">
-        <v>43.14648564339256</v>
+        <v>43.15751128969607</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86955018756407</v>
+        <v>99.86914677933119</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.3659386696506</v>
+        <v>82.26966996796743</v>
       </c>
       <c r="C11" t="n">
-        <v>37.69580322132855</v>
+        <v>39.59127265988737</v>
       </c>
       <c r="D11" t="n">
-        <v>1.65082377459883</v>
+        <v>1.741816663170841</v>
       </c>
       <c r="E11" t="n">
-        <v>9.822913775556621</v>
+        <v>10.23109727078132</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530751371693369</v>
+        <v>0.7530145254647755</v>
       </c>
       <c r="G11" t="n">
-        <v>25.52013002201829</v>
+        <v>26.91797173466848</v>
       </c>
       <c r="H11" t="n">
-        <v>34.6414563097895</v>
+        <v>34.63866817137966</v>
       </c>
       <c r="I11" t="n">
-        <v>3.270820043209665</v>
+        <v>3.280760818347495</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706719607308356</v>
+        <v>4.706340784154847</v>
       </c>
       <c r="K11" t="n">
-        <v>19.63406133034939</v>
+        <v>17.73033003203256</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56125582357947</v>
+        <v>42.56918378850946</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89112037525743</v>
+        <v>99.8907864804294</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.90827126099691</v>
+        <v>79.94104469766687</v>
       </c>
       <c r="C12" t="n">
-        <v>35.7435558622463</v>
+        <v>37.77093614855531</v>
       </c>
       <c r="D12" t="n">
-        <v>1.542951577764796</v>
+        <v>1.639392787077947</v>
       </c>
       <c r="E12" t="n">
-        <v>9.635851686432643</v>
+        <v>10.08566031983191</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539543938127352</v>
+        <v>0.7538739366035078</v>
       </c>
       <c r="G12" t="n">
-        <v>23.85253077167778</v>
+        <v>25.33511685681657</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68190211538582</v>
+        <v>34.67820108376135</v>
       </c>
       <c r="I12" t="n">
-        <v>2.728865754593545</v>
+        <v>2.737087609803647</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712214961329596</v>
+        <v>4.711712103771924</v>
       </c>
       <c r="K12" t="n">
-        <v>22.09172873900307</v>
+        <v>20.05895530233315</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07385928643924</v>
+        <v>42.07897630415742</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90914388768861</v>
+        <v>99.90886775504589</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.46267603802373</v>
+        <v>77.64255433558218</v>
       </c>
       <c r="C13" t="n">
-        <v>33.71870233929717</v>
+        <v>35.89570459516243</v>
       </c>
       <c r="D13" t="n">
-        <v>1.436678718149422</v>
+        <v>1.5392240829135</v>
       </c>
       <c r="E13" t="n">
-        <v>9.351559704009858</v>
+        <v>9.849939049132264</v>
       </c>
       <c r="F13" t="n">
-        <v>0.754712498201051</v>
+        <v>0.7546128790197574</v>
       </c>
       <c r="G13" t="n">
-        <v>22.20965571927849</v>
+        <v>23.78711332440778</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71677491724834</v>
+        <v>34.71219243490884</v>
       </c>
       <c r="I13" t="n">
-        <v>2.27634136737998</v>
+        <v>2.283142071326547</v>
       </c>
       <c r="J13" t="n">
-        <v>4.71695311375657</v>
+        <v>4.716330493873484</v>
       </c>
       <c r="K13" t="n">
-        <v>24.53732396197629</v>
+        <v>22.35744566441783</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66817187221003</v>
+        <v>41.67081952903632</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92419817348349</v>
+        <v>99.92396978861657</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.79993730122857</v>
+        <v>84.12333320655326</v>
       </c>
       <c r="C14" t="n">
-        <v>38.17557684126062</v>
+        <v>39.88562523174275</v>
       </c>
       <c r="D14" t="n">
-        <v>1.438494758093589</v>
+        <v>1.541044282392572</v>
       </c>
       <c r="E14" t="n">
-        <v>11.83932016827628</v>
+        <v>12.08999206094584</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556664957968811</v>
+        <v>0.7555052415968116</v>
       </c>
       <c r="G14" t="n">
-        <v>24.19035142202585</v>
+        <v>25.54625013482912</v>
       </c>
       <c r="H14" t="n">
-        <v>36.7132802980838</v>
+        <v>36.48424862693712</v>
       </c>
       <c r="I14" t="n">
-        <v>3.139908560221664</v>
+        <v>2.984385099871736</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722915598730507</v>
+        <v>4.721907759980073</v>
       </c>
       <c r="K14" t="n">
-        <v>17.20006269877144</v>
+        <v>15.87666679344674</v>
       </c>
       <c r="L14" t="n">
-        <v>44.51982897476962</v>
+        <v>44.13834597137565</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89546851480168</v>
+        <v>99.90063799656514</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.01307633375178</v>
+        <v>83.45611783179305</v>
       </c>
       <c r="C15" t="n">
-        <v>37.87307028785772</v>
+        <v>39.68007427554186</v>
       </c>
       <c r="D15" t="n">
-        <v>1.409784521378797</v>
+        <v>1.516305462127369</v>
       </c>
       <c r="E15" t="n">
-        <v>12.03958746405507</v>
+        <v>12.31081806845312</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564709914021498</v>
+        <v>0.7562564549138495</v>
       </c>
       <c r="G15" t="n">
-        <v>23.70754763589264</v>
+        <v>25.13614894711096</v>
       </c>
       <c r="H15" t="n">
-        <v>36.7523658904967</v>
+        <v>36.52052561341142</v>
       </c>
       <c r="I15" t="n">
-        <v>2.619376134262974</v>
+        <v>2.48946044256476</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727943696263437</v>
+        <v>4.72660284321156</v>
       </c>
       <c r="K15" t="n">
-        <v>17.98692366624821</v>
+        <v>16.54388216820696</v>
       </c>
       <c r="L15" t="n">
-        <v>44.05278636366569</v>
+        <v>43.69314397014364</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91278031777163</v>
+        <v>99.91710041389246</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.54120251156802</v>
+        <v>81.14920707635389</v>
       </c>
       <c r="C16" t="n">
-        <v>35.80531903141477</v>
+        <v>37.75837657196681</v>
       </c>
       <c r="D16" t="n">
-        <v>1.317203150166132</v>
+        <v>1.427745746929058</v>
       </c>
       <c r="E16" t="n">
-        <v>11.61307607228665</v>
+        <v>11.93785887996894</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7571636080803669</v>
+        <v>0.756901452050635</v>
       </c>
       <c r="G16" t="n">
-        <v>22.15065916468578</v>
+        <v>23.66807391372335</v>
       </c>
       <c r="H16" t="n">
-        <v>36.78601596018743</v>
+        <v>36.55167329393897</v>
       </c>
       <c r="I16" t="n">
-        <v>2.184812005659372</v>
+        <v>2.076319714426476</v>
       </c>
       <c r="J16" t="n">
-        <v>4.732272550502294</v>
+        <v>4.730634075316469</v>
       </c>
       <c r="K16" t="n">
-        <v>20.45879748843196</v>
+        <v>18.85079292364611</v>
       </c>
       <c r="L16" t="n">
-        <v>43.66312303197929</v>
+        <v>43.32167882542695</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92723955182603</v>
+        <v>99.93084832103987</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.40659187197627</v>
+        <v>82.76375989832707</v>
       </c>
       <c r="C17" t="n">
-        <v>37.14494471178</v>
+        <v>38.93610965222605</v>
       </c>
       <c r="D17" t="n">
-        <v>1.31839075777646</v>
+        <v>1.428940734367597</v>
       </c>
       <c r="E17" t="n">
-        <v>12.46105018863146</v>
+        <v>12.69427277496455</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7578462767052533</v>
+        <v>0.7575349596127187</v>
       </c>
       <c r="G17" t="n">
-        <v>22.64114785727047</v>
+        <v>24.08794973207571</v>
       </c>
       <c r="H17" t="n">
-        <v>37.28970008212409</v>
+        <v>36.98233236235924</v>
       </c>
       <c r="I17" t="n">
-        <v>2.201917480060707</v>
+        <v>2.07813583736775</v>
       </c>
       <c r="J17" t="n">
-        <v>4.736539229407834</v>
+        <v>4.734593497579492</v>
       </c>
       <c r="K17" t="n">
-        <v>18.59340812802373</v>
+        <v>17.23624010167293</v>
       </c>
       <c r="L17" t="n">
-        <v>44.18831602717079</v>
+        <v>43.7584369812916</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92666886697452</v>
+        <v>99.93078673519058</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.07520614627023</v>
+        <v>80.51791385009207</v>
       </c>
       <c r="C18" t="n">
-        <v>35.15287122690827</v>
+        <v>37.01148213019776</v>
       </c>
       <c r="D18" t="n">
-        <v>1.234952037347238</v>
+        <v>1.345920241713912</v>
       </c>
       <c r="E18" t="n">
-        <v>11.97847001288231</v>
+        <v>12.24558114512958</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7584329217167167</v>
+        <v>0.7580784515038316</v>
       </c>
       <c r="G18" t="n">
-        <v>21.20822791671687</v>
+        <v>22.68845610321002</v>
       </c>
       <c r="H18" t="n">
-        <v>37.3185658524057</v>
+        <v>37.00886526027812</v>
       </c>
       <c r="I18" t="n">
-        <v>1.836351644471938</v>
+        <v>1.733022326357676</v>
       </c>
       <c r="J18" t="n">
-        <v>4.740205760729481</v>
+        <v>4.737990321898947</v>
       </c>
       <c r="K18" t="n">
-        <v>20.92479385372975</v>
+        <v>19.48208614990794</v>
       </c>
       <c r="L18" t="n">
-        <v>43.86117054491584</v>
+        <v>43.44870572441186</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93883562555386</v>
+        <v>99.94227400451754</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.18465298627092</v>
+        <v>79.66034741295542</v>
       </c>
       <c r="C19" t="n">
-        <v>34.5445785681738</v>
+        <v>36.42116704974815</v>
       </c>
       <c r="D19" t="n">
-        <v>1.203786876316018</v>
+        <v>1.314900698306904</v>
       </c>
       <c r="E19" t="n">
-        <v>11.93139755171396</v>
+        <v>12.20419923746323</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7589280667747539</v>
+        <v>0.7585368425653201</v>
       </c>
       <c r="G19" t="n">
-        <v>20.67301859827962</v>
+        <v>22.16555323934097</v>
       </c>
       <c r="H19" t="n">
-        <v>37.34292938268735</v>
+        <v>37.03124359460156</v>
       </c>
       <c r="I19" t="n">
-        <v>1.531292093157004</v>
+        <v>1.445058534644191</v>
       </c>
       <c r="J19" t="n">
-        <v>4.743300417342213</v>
+        <v>4.74085526603325</v>
       </c>
       <c r="K19" t="n">
-        <v>21.81534701372908</v>
+        <v>20.33965258704457</v>
       </c>
       <c r="L19" t="n">
-        <v>43.58906465019513</v>
+        <v>43.1910408541418</v>
       </c>
       <c r="M19" t="n">
-        <v>99.948990232098</v>
+        <v>99.95186049093452</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.65141993257174</v>
+        <v>77.21004258783397</v>
       </c>
       <c r="C20" t="n">
-        <v>32.2465774967681</v>
+        <v>34.19358776681112</v>
       </c>
       <c r="D20" t="n">
-        <v>1.114214160981413</v>
+        <v>1.225249365859166</v>
       </c>
       <c r="E20" t="n">
-        <v>11.256391933073</v>
+        <v>11.57291088431015</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7593550229756855</v>
+        <v>0.7589314013061799</v>
       </c>
       <c r="G20" t="n">
-        <v>19.13475759341004</v>
+        <v>20.65428217156609</v>
       </c>
       <c r="H20" t="n">
-        <v>37.36393769158894</v>
+        <v>37.05050567921665</v>
       </c>
       <c r="I20" t="n">
-        <v>1.276794636944639</v>
+        <v>1.204841827412106</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745968893598035</v>
+        <v>4.743321258163625</v>
       </c>
       <c r="K20" t="n">
-        <v>24.34858006742825</v>
+        <v>22.78995741216601</v>
       </c>
       <c r="L20" t="n">
-        <v>43.36230654432707</v>
+        <v>42.97631430617163</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95746410852342</v>
+        <v>99.95985948514877</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.7563591265683</v>
+        <v>82.74237743332858</v>
       </c>
       <c r="C21" t="n">
-        <v>35.98915620527208</v>
+        <v>37.58334145775563</v>
       </c>
       <c r="D21" t="n">
-        <v>1.11507321446986</v>
+        <v>1.22612247783933</v>
       </c>
       <c r="E21" t="n">
-        <v>13.2863094125533</v>
+        <v>13.41574840645047</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7599404818616887</v>
+        <v>0.759472215378047</v>
       </c>
       <c r="G21" t="n">
-        <v>20.85558055398298</v>
+        <v>22.20878022518824</v>
       </c>
       <c r="H21" t="n">
-        <v>39.09881525791297</v>
+        <v>38.61668767210281</v>
       </c>
       <c r="I21" t="n">
-        <v>1.891012194151935</v>
+        <v>1.768865090256879</v>
       </c>
       <c r="J21" t="n">
-        <v>4.749628011635555</v>
+        <v>4.746701346112794</v>
       </c>
       <c r="K21" t="n">
-        <v>18.24364087343172</v>
+        <v>17.25762256667143</v>
       </c>
       <c r="L21" t="n">
-        <v>45.70421774274556</v>
+        <v>45.10011579238571</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93701482144935</v>
+        <v>99.94107981681277</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_72_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_72_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.63786182817462</v>
+        <v>45.2567080386869</v>
       </c>
       <c r="M2" t="n">
-        <v>98.79358371536202</v>
+        <v>99.73387023429351</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.06808539073904</v>
+        <v>88.04939291445017</v>
       </c>
       <c r="C3" t="n">
-        <v>45.9361494010403</v>
+        <v>45.93945618638051</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228829513010365</v>
+        <v>2.22877908461466</v>
       </c>
       <c r="E3" t="n">
-        <v>5.712882911122991</v>
+        <v>5.713702526824227</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429431710034549</v>
+        <v>0.7429263615382201</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97528002948486</v>
+        <v>33.97663332151308</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17538586615892</v>
+        <v>34.17461263075812</v>
       </c>
       <c r="I3" t="n">
-        <v>6.589369081186859</v>
+        <v>6.569449229587984</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643394818771593</v>
+        <v>4.643289759613875</v>
       </c>
       <c r="K3" t="n">
-        <v>11.93191460926096</v>
+        <v>11.95060708554982</v>
       </c>
       <c r="L3" t="n">
-        <v>48.89542192551491</v>
+        <v>48.87413231748678</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7634859358162</v>
+        <v>106.7641955894171</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.29232983207825</v>
+        <v>87.19085717420826</v>
       </c>
       <c r="C4" t="n">
-        <v>42.79937021612571</v>
+        <v>42.71592905835773</v>
       </c>
       <c r="D4" t="n">
-        <v>2.192177327926861</v>
+        <v>2.187710707307366</v>
       </c>
       <c r="E4" t="n">
-        <v>6.536050089767441</v>
+        <v>6.522756703806289</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445042771912533</v>
+        <v>0.7444845184254723</v>
       </c>
       <c r="G4" t="n">
-        <v>33.41657051642631</v>
+        <v>33.35056624895676</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24719675079765</v>
+        <v>34.24628784757171</v>
       </c>
       <c r="I4" t="n">
-        <v>5.502679137523385</v>
+        <v>5.486022907981471</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653151732445333</v>
+        <v>4.653028240159201</v>
       </c>
       <c r="K4" t="n">
-        <v>12.70767016792176</v>
+        <v>12.80914282579172</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30992158591956</v>
+        <v>44.29244341502864</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81696196996704</v>
+        <v>99.8175152991781</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.22427890934894</v>
+        <v>86.19778115710604</v>
       </c>
       <c r="C5" t="n">
-        <v>42.58551227990525</v>
+        <v>42.57438978750221</v>
       </c>
       <c r="D5" t="n">
-        <v>2.140416638858728</v>
+        <v>2.139841113392246</v>
       </c>
       <c r="E5" t="n">
-        <v>7.147342086769423</v>
+        <v>7.143328445176155</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458264246185063</v>
+        <v>0.7458030276465486</v>
       </c>
       <c r="G5" t="n">
-        <v>32.62755372741508</v>
+        <v>32.62081799757949</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30801553245129</v>
+        <v>34.30693927174123</v>
       </c>
       <c r="I5" t="n">
-        <v>4.593709345370264</v>
+        <v>4.579782378779456</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661415153865664</v>
+        <v>4.661268922790928</v>
       </c>
       <c r="K5" t="n">
-        <v>13.77572109065107</v>
+        <v>13.80221884289394</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48591443117913</v>
+        <v>43.47100184438214</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84714780173545</v>
+        <v>99.84761047477829</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.01219960608788</v>
+        <v>85.03909664115099</v>
       </c>
       <c r="C6" t="n">
-        <v>42.08707476125765</v>
+        <v>42.12718695378095</v>
       </c>
       <c r="D6" t="n">
-        <v>2.081646029093897</v>
+        <v>2.083789794675372</v>
       </c>
       <c r="E6" t="n">
-        <v>7.590067826234931</v>
+        <v>7.593248900962417</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469475905423629</v>
+        <v>0.7469204002638344</v>
       </c>
       <c r="G6" t="n">
-        <v>31.73168084319129</v>
+        <v>31.76634340367428</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35958916494869</v>
+        <v>34.35833841213638</v>
       </c>
       <c r="I6" t="n">
-        <v>3.833845711186933</v>
+        <v>3.822203227789749</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668422440889768</v>
+        <v>4.668252501648965</v>
       </c>
       <c r="K6" t="n">
-        <v>14.98780039391213</v>
+        <v>14.96090335884902</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79752180745884</v>
+        <v>42.7846935101817</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87239696262861</v>
+        <v>99.87278382281167</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.6182174459135</v>
+        <v>83.63344026988548</v>
       </c>
       <c r="C7" t="n">
-        <v>41.28883869988631</v>
+        <v>41.31550768772564</v>
       </c>
       <c r="D7" t="n">
-        <v>2.014125713430605</v>
+        <v>2.015671718279108</v>
       </c>
       <c r="E7" t="n">
-        <v>7.877033819573924</v>
+        <v>7.876565624686129</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479001121222681</v>
+        <v>0.7478698179525405</v>
       </c>
       <c r="G7" t="n">
-        <v>30.70243135643213</v>
+        <v>30.72791706512004</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40340515762433</v>
+        <v>34.40201162581685</v>
       </c>
       <c r="I7" t="n">
-        <v>3.198945585966074</v>
+        <v>3.189218055827437</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674375700764175</v>
+        <v>4.674186362203377</v>
       </c>
       <c r="K7" t="n">
-        <v>16.38178255408648</v>
+        <v>16.36655973011452</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22288303182757</v>
+        <v>42.2117602702768</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89350428580038</v>
+        <v>99.89382768811696</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.44743595402461</v>
+        <v>88.64397792976929</v>
       </c>
       <c r="C8" t="n">
-        <v>43.55131649670006</v>
+        <v>43.66504627314828</v>
       </c>
       <c r="D8" t="n">
-        <v>2.018408842781888</v>
+        <v>2.0200107811699</v>
       </c>
       <c r="E8" t="n">
-        <v>9.683613663319187</v>
+        <v>9.746200151220409</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494905555095395</v>
+        <v>0.7494797299956545</v>
       </c>
       <c r="G8" t="n">
-        <v>31.19241727777572</v>
+        <v>31.24335176112272</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47656555343881</v>
+        <v>34.4760675798001</v>
       </c>
       <c r="I8" t="n">
-        <v>5.642624089264838</v>
+        <v>5.724619613987662</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684315971934621</v>
+        <v>4.68424831247284</v>
       </c>
       <c r="K8" t="n">
-        <v>11.55256404597541</v>
+        <v>11.3560220702307</v>
       </c>
       <c r="L8" t="n">
-        <v>44.70843111542335</v>
+        <v>44.78852089311777</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81231165809882</v>
+        <v>99.80958923649676</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.56793994429653</v>
+        <v>86.87879681782168</v>
       </c>
       <c r="C9" t="n">
-        <v>42.54813211983392</v>
+        <v>42.78894736905936</v>
       </c>
       <c r="D9" t="n">
-        <v>1.933469408795101</v>
+        <v>1.940658366931722</v>
       </c>
       <c r="E9" t="n">
-        <v>10.06122354421283</v>
+        <v>10.15988257403021</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508500415240487</v>
+        <v>0.7508540436445185</v>
       </c>
       <c r="G9" t="n">
-        <v>29.87976633605556</v>
+        <v>30.01601405864676</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53910191010623</v>
+        <v>34.53928600764785</v>
       </c>
       <c r="I9" t="n">
-        <v>4.710715944077448</v>
+        <v>4.779263994142399</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692812759525304</v>
+        <v>4.69283777277824</v>
       </c>
       <c r="K9" t="n">
-        <v>13.43206005570349</v>
+        <v>13.12120318217831</v>
       </c>
       <c r="L9" t="n">
-        <v>43.86306826642746</v>
+        <v>43.93083223726266</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84326044196487</v>
+        <v>99.84098278850033</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.47729581325036</v>
+        <v>84.90886128784612</v>
       </c>
       <c r="C10" t="n">
-        <v>41.18893130288546</v>
+        <v>41.56126017913074</v>
       </c>
       <c r="D10" t="n">
-        <v>1.839787882796201</v>
+        <v>1.852784006802295</v>
       </c>
       <c r="E10" t="n">
-        <v>10.22901271025092</v>
+        <v>10.36466216700695</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520148938065251</v>
+        <v>0.7520298629589789</v>
       </c>
       <c r="G10" t="n">
-        <v>28.43201542046355</v>
+        <v>28.65686807294208</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59268511510015</v>
+        <v>34.59337369611303</v>
       </c>
       <c r="I10" t="n">
-        <v>3.931686704542237</v>
+        <v>3.988956838529161</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700093086290781</v>
+        <v>4.700186643493617</v>
       </c>
       <c r="K10" t="n">
-        <v>15.52270418674964</v>
+        <v>15.0911387121539</v>
       </c>
       <c r="L10" t="n">
-        <v>43.15751128969607</v>
+        <v>43.21484377554475</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86914677933119</v>
+        <v>99.86724266682938</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.26966996796743</v>
+        <v>82.72329263819391</v>
       </c>
       <c r="C11" t="n">
-        <v>39.59127265988737</v>
+        <v>39.99479724318715</v>
       </c>
       <c r="D11" t="n">
-        <v>1.741816663170841</v>
+        <v>1.75606695920309</v>
       </c>
       <c r="E11" t="n">
-        <v>10.23109727078132</v>
+        <v>10.37838203359949</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530145254647755</v>
+        <v>0.7530385262599142</v>
       </c>
       <c r="G11" t="n">
-        <v>26.91797173466848</v>
+        <v>27.16095291862337</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63866817137966</v>
+        <v>34.63977220795605</v>
       </c>
       <c r="I11" t="n">
-        <v>3.280760818347495</v>
+        <v>3.328589203427525</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706340784154847</v>
+        <v>4.706490789124463</v>
       </c>
       <c r="K11" t="n">
-        <v>17.73033003203256</v>
+        <v>17.2767073618061</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56918378850946</v>
+        <v>42.61769103838095</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8907864804294</v>
+        <v>99.88919564337419</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.94104469766687</v>
+        <v>80.29866411987827</v>
       </c>
       <c r="C12" t="n">
-        <v>37.77093614855531</v>
+        <v>38.08611597540184</v>
       </c>
       <c r="D12" t="n">
-        <v>1.639392787077947</v>
+        <v>1.649612524834118</v>
       </c>
       <c r="E12" t="n">
-        <v>10.08566031983191</v>
+        <v>10.21207172682262</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538739366035078</v>
+        <v>0.7539066206233844</v>
       </c>
       <c r="G12" t="n">
-        <v>25.33511685681657</v>
+        <v>25.51443035026614</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67820108376135</v>
+        <v>34.67970454867568</v>
       </c>
       <c r="I12" t="n">
-        <v>2.737087609803647</v>
+        <v>2.777021969760176</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711712103771924</v>
+        <v>4.711916378896152</v>
       </c>
       <c r="K12" t="n">
-        <v>20.05895530233315</v>
+        <v>19.70133588012172</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07897630415742</v>
+        <v>42.12008733327012</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90886775504589</v>
+        <v>99.90753918879368</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.64255433558218</v>
+        <v>77.84466499719575</v>
       </c>
       <c r="C13" t="n">
-        <v>35.89570459516243</v>
+        <v>36.06171959566376</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5392240829135</v>
+        <v>1.542832967994682</v>
       </c>
       <c r="E13" t="n">
-        <v>9.849939049132264</v>
+        <v>9.937123547505175</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546128790197574</v>
+        <v>0.7546544389287227</v>
       </c>
       <c r="G13" t="n">
-        <v>23.78711332440778</v>
+        <v>23.86287913760423</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71219243490884</v>
+        <v>34.71410419072124</v>
       </c>
       <c r="I13" t="n">
-        <v>2.283142071326547</v>
+        <v>2.316480471137165</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716330493873484</v>
+        <v>4.716590243304517</v>
       </c>
       <c r="K13" t="n">
-        <v>22.35744566441783</v>
+        <v>22.15533500280426</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67081952903632</v>
+        <v>41.70580590237198</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92396978861657</v>
+        <v>99.92286050083999</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.12333320655326</v>
+        <v>84.34352939913876</v>
       </c>
       <c r="C14" t="n">
-        <v>39.88562523174275</v>
+        <v>39.9238101826372</v>
       </c>
       <c r="D14" t="n">
-        <v>1.541044282392572</v>
+        <v>1.544809689958298</v>
       </c>
       <c r="E14" t="n">
-        <v>12.08999206094584</v>
+        <v>12.13562490493632</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555052415968116</v>
+        <v>0.7556213238963868</v>
       </c>
       <c r="G14" t="n">
-        <v>25.54625013482912</v>
+        <v>25.53890579748358</v>
       </c>
       <c r="H14" t="n">
-        <v>36.48424862693712</v>
+        <v>36.40403375217167</v>
       </c>
       <c r="I14" t="n">
-        <v>2.984385099871736</v>
+        <v>3.241900656340095</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721907759980073</v>
+        <v>4.722633274352417</v>
       </c>
       <c r="K14" t="n">
-        <v>15.87666679344674</v>
+        <v>15.65647060086122</v>
       </c>
       <c r="L14" t="n">
-        <v>44.13834597137565</v>
+        <v>44.31179413800426</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90063799656514</v>
+        <v>99.89207492150268</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.45611783179305</v>
+        <v>83.51518959115758</v>
       </c>
       <c r="C15" t="n">
-        <v>39.68007427554186</v>
+        <v>39.58994493207159</v>
       </c>
       <c r="D15" t="n">
-        <v>1.516305462127369</v>
+        <v>1.512993472236739</v>
       </c>
       <c r="E15" t="n">
-        <v>12.31081806845312</v>
+        <v>12.34338340075851</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562564549138495</v>
+        <v>0.7564369750964361</v>
       </c>
       <c r="G15" t="n">
-        <v>25.13614894711096</v>
+        <v>25.0198662279899</v>
       </c>
       <c r="H15" t="n">
-        <v>36.52052561341142</v>
+        <v>36.45027833087259</v>
       </c>
       <c r="I15" t="n">
-        <v>2.48946044256476</v>
+        <v>2.704500089850692</v>
       </c>
       <c r="J15" t="n">
-        <v>4.72660284321156</v>
+        <v>4.727731094352725</v>
       </c>
       <c r="K15" t="n">
-        <v>16.54388216820696</v>
+        <v>16.48481040884242</v>
       </c>
       <c r="L15" t="n">
-        <v>43.69314397014364</v>
+        <v>43.83519186307653</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91710041389246</v>
+        <v>99.90994720399054</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.14920707635389</v>
+        <v>80.96348986314152</v>
       </c>
       <c r="C16" t="n">
-        <v>37.75837657196681</v>
+        <v>37.45660536054479</v>
       </c>
       <c r="D16" t="n">
-        <v>1.427745746929058</v>
+        <v>1.414998867046229</v>
       </c>
       <c r="E16" t="n">
-        <v>11.93785887996894</v>
+        <v>11.91989250150116</v>
       </c>
       <c r="F16" t="n">
-        <v>0.756901452050635</v>
+        <v>0.7571395153164043</v>
       </c>
       <c r="G16" t="n">
-        <v>23.66807391372335</v>
+        <v>23.39936226817665</v>
       </c>
       <c r="H16" t="n">
-        <v>36.55167329393897</v>
+        <v>36.48413149696512</v>
       </c>
       <c r="I16" t="n">
-        <v>2.076319714426476</v>
+        <v>2.255843243408427</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730634075316469</v>
+        <v>4.732121970727526</v>
       </c>
       <c r="K16" t="n">
-        <v>18.85079292364611</v>
+        <v>19.03651013685848</v>
       </c>
       <c r="L16" t="n">
-        <v>43.32167882542695</v>
+        <v>43.43175950010089</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93084832103987</v>
+        <v>99.92487499750416</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.76375989832707</v>
+        <v>82.56430803473228</v>
       </c>
       <c r="C17" t="n">
-        <v>38.93610965222605</v>
+        <v>38.60894806962081</v>
       </c>
       <c r="D17" t="n">
-        <v>1.428940734367597</v>
+        <v>1.416311198453052</v>
       </c>
       <c r="E17" t="n">
-        <v>12.69427277496455</v>
+        <v>12.68167753399726</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575349596127187</v>
+        <v>0.7578417193876841</v>
       </c>
       <c r="G17" t="n">
-        <v>24.08794973207571</v>
+        <v>23.7889252331217</v>
       </c>
       <c r="H17" t="n">
-        <v>36.98233236235924</v>
+        <v>36.88582984520259</v>
       </c>
       <c r="I17" t="n">
-        <v>2.07813583736775</v>
+        <v>2.297211758396966</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734593497579492</v>
+        <v>4.736510746173025</v>
       </c>
       <c r="K17" t="n">
-        <v>17.23624010167293</v>
+        <v>17.43569196526771</v>
       </c>
       <c r="L17" t="n">
-        <v>43.7584369812916</v>
+        <v>43.87885719182626</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93078673519058</v>
+        <v>99.9234972267148</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.51791385009207</v>
+        <v>80.16514244752506</v>
       </c>
       <c r="C18" t="n">
-        <v>37.01148213019776</v>
+        <v>36.5646472864187</v>
       </c>
       <c r="D18" t="n">
-        <v>1.345920241713912</v>
+        <v>1.327680994382185</v>
       </c>
       <c r="E18" t="n">
-        <v>12.24558114512958</v>
+        <v>12.20739235363667</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580784515038316</v>
+        <v>0.7584454418112535</v>
       </c>
       <c r="G18" t="n">
-        <v>22.68845610321002</v>
+        <v>22.30025713507864</v>
       </c>
       <c r="H18" t="n">
-        <v>37.00886526027812</v>
+        <v>36.91521434861514</v>
       </c>
       <c r="I18" t="n">
-        <v>1.733022326357676</v>
+        <v>1.915868162680827</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737990321898947</v>
+        <v>4.740284011320334</v>
       </c>
       <c r="K18" t="n">
-        <v>19.48208614990794</v>
+        <v>19.83485755247495</v>
       </c>
       <c r="L18" t="n">
-        <v>43.44870572441186</v>
+        <v>43.53668372337309</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94227400451754</v>
+        <v>99.93618856226674</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.66034741295542</v>
+        <v>79.18117599346665</v>
       </c>
       <c r="C19" t="n">
-        <v>36.42116704974815</v>
+        <v>35.87590227122269</v>
       </c>
       <c r="D19" t="n">
-        <v>1.314900698306904</v>
+        <v>1.292093962406644</v>
       </c>
       <c r="E19" t="n">
-        <v>12.20419923746323</v>
+        <v>12.1464583633654</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585368425653201</v>
+        <v>0.7589555443795174</v>
       </c>
       <c r="G19" t="n">
-        <v>22.16555323934097</v>
+        <v>21.70252321624816</v>
       </c>
       <c r="H19" t="n">
-        <v>37.03124359460156</v>
+        <v>36.94004216695138</v>
       </c>
       <c r="I19" t="n">
-        <v>1.445058534644191</v>
+        <v>1.597630587743569</v>
       </c>
       <c r="J19" t="n">
-        <v>4.74085526603325</v>
+        <v>4.743472152371983</v>
       </c>
       <c r="K19" t="n">
-        <v>20.33965258704457</v>
+        <v>20.81882400653335</v>
       </c>
       <c r="L19" t="n">
-        <v>43.1910408541418</v>
+        <v>43.25205516216949</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95186049093452</v>
+        <v>99.94678143992552</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.21004258783397</v>
+        <v>76.57694294579633</v>
       </c>
       <c r="C20" t="n">
-        <v>34.19358776681112</v>
+        <v>33.51769117591603</v>
       </c>
       <c r="D20" t="n">
-        <v>1.225249365859166</v>
+        <v>1.197033244984051</v>
       </c>
       <c r="E20" t="n">
-        <v>11.57291088431015</v>
+        <v>11.47485239889507</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589314013061799</v>
+        <v>0.7593956368505522</v>
       </c>
       <c r="G20" t="n">
-        <v>20.65428217156609</v>
+        <v>20.10584566272535</v>
       </c>
       <c r="H20" t="n">
-        <v>37.05050567921665</v>
+        <v>36.96146243926874</v>
       </c>
       <c r="I20" t="n">
-        <v>1.204841827412106</v>
+        <v>1.332130832756622</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743321258163625</v>
+        <v>4.746222730315951</v>
       </c>
       <c r="K20" t="n">
-        <v>22.78995741216601</v>
+        <v>23.42305705420366</v>
       </c>
       <c r="L20" t="n">
-        <v>42.97631430617163</v>
+        <v>43.01487314244301</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95985948514877</v>
+        <v>99.95562137256269</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.74237743332858</v>
+        <v>82.5194225296941</v>
       </c>
       <c r="C21" t="n">
-        <v>37.58334145775563</v>
+        <v>37.05584315924338</v>
       </c>
       <c r="D21" t="n">
-        <v>1.22612247783933</v>
+        <v>1.198050315778372</v>
       </c>
       <c r="E21" t="n">
-        <v>13.41574840645047</v>
+        <v>13.42073863077914</v>
       </c>
       <c r="F21" t="n">
-        <v>0.759472215378047</v>
+        <v>0.7600408646475345</v>
       </c>
       <c r="G21" t="n">
-        <v>22.20878022518824</v>
+        <v>21.70849820110664</v>
       </c>
       <c r="H21" t="n">
-        <v>38.61668767210281</v>
+        <v>38.57843651434547</v>
       </c>
       <c r="I21" t="n">
-        <v>1.768865090256879</v>
+        <v>2.103402598989839</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746701346112794</v>
+        <v>4.75025540404709</v>
       </c>
       <c r="K21" t="n">
-        <v>17.25762256667143</v>
+        <v>17.48057747030588</v>
       </c>
       <c r="L21" t="n">
-        <v>45.10011579238571</v>
+        <v>45.39352547245172</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94107981681277</v>
+        <v>99.929946102001</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_72_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_72_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.2567080386869</v>
+        <v>44.43194187789938</v>
       </c>
       <c r="M2" t="n">
-        <v>99.73387023429351</v>
+        <v>92.24296190979712</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.04939291445017</v>
+        <v>81.39005492686226</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93945618638051</v>
+        <v>43.14561048241781</v>
       </c>
       <c r="D3" t="n">
-        <v>2.22877908461466</v>
+        <v>2.17575237691555</v>
       </c>
       <c r="E3" t="n">
-        <v>5.713702526824227</v>
+        <v>4.138456478084826</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429263615382201</v>
+        <v>0.7375716238448269</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97663332151308</v>
+        <v>32.72694200277141</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17461263075812</v>
+        <v>33.92829469686203</v>
       </c>
       <c r="I3" t="n">
-        <v>6.569449229587984</v>
+        <v>3.073215099353445</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643289759613875</v>
+        <v>4.609822649030168</v>
       </c>
       <c r="K3" t="n">
-        <v>11.95060708554982</v>
+        <v>18.60994507313774</v>
       </c>
       <c r="L3" t="n">
-        <v>48.87413231748678</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7641955894171</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.19085717420826</v>
+        <v>88.3394057688154</v>
       </c>
       <c r="C4" t="n">
-        <v>42.71592905835773</v>
+        <v>42.72904433246093</v>
       </c>
       <c r="D4" t="n">
-        <v>2.187710707307366</v>
+        <v>2.181385815432688</v>
       </c>
       <c r="E4" t="n">
-        <v>6.522756703806289</v>
+        <v>6.502358257849971</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444845184254723</v>
+        <v>0.7394813376702603</v>
       </c>
       <c r="G4" t="n">
-        <v>33.35056624895676</v>
+        <v>33.41645257940809</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24628784757171</v>
+        <v>34.01614153283197</v>
       </c>
       <c r="I4" t="n">
-        <v>5.486022907981471</v>
+        <v>6.861827885183282</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653028240159201</v>
+        <v>4.621758360439126</v>
       </c>
       <c r="K4" t="n">
-        <v>12.80914282579172</v>
+        <v>11.6605942311846</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29244341502864</v>
+        <v>45.38222453021052</v>
       </c>
       <c r="M4" t="n">
-        <v>99.8175152991781</v>
+        <v>99.77186309385606</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.19778115710604</v>
+        <v>86.97096875240572</v>
       </c>
       <c r="C5" t="n">
-        <v>42.57438978750221</v>
+        <v>42.42427262467123</v>
       </c>
       <c r="D5" t="n">
-        <v>2.139841113392246</v>
+        <v>2.115116926107792</v>
       </c>
       <c r="E5" t="n">
-        <v>7.143328445176155</v>
+        <v>7.259946329102529</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458030276465486</v>
+        <v>0.7411055510297005</v>
       </c>
       <c r="G5" t="n">
-        <v>32.62081799757949</v>
+        <v>32.40128544026715</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30693927174123</v>
+        <v>34.09085534736622</v>
       </c>
       <c r="I5" t="n">
-        <v>4.579782378779456</v>
+        <v>5.730749464596707</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661268922790928</v>
+        <v>4.631909693935628</v>
       </c>
       <c r="K5" t="n">
-        <v>13.80221884289394</v>
+        <v>13.02903124759428</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47100184438214</v>
+        <v>44.35608979759049</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84761047477829</v>
+        <v>99.80939366985601</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.03909664115099</v>
+        <v>85.26285486633775</v>
       </c>
       <c r="C6" t="n">
-        <v>42.12718695378095</v>
+        <v>41.60527778607762</v>
       </c>
       <c r="D6" t="n">
-        <v>2.083789794675372</v>
+        <v>2.03243051090823</v>
       </c>
       <c r="E6" t="n">
-        <v>7.593248900962417</v>
+        <v>7.773558971768503</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469204002638344</v>
+        <v>0.7424917983268251</v>
       </c>
       <c r="G6" t="n">
-        <v>31.76634340367428</v>
+        <v>31.13461970285869</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35833841213638</v>
+        <v>34.15462272303395</v>
       </c>
       <c r="I6" t="n">
-        <v>3.822203227789749</v>
+        <v>4.784557419898899</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668252501648965</v>
+        <v>4.640573739542656</v>
       </c>
       <c r="K6" t="n">
-        <v>14.96090335884902</v>
+        <v>14.73714513366227</v>
       </c>
       <c r="L6" t="n">
-        <v>42.7846935101817</v>
+        <v>43.49838959513243</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87278382281167</v>
+        <v>99.84081251487231</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.63344026988548</v>
+        <v>83.39078683313497</v>
       </c>
       <c r="C7" t="n">
-        <v>41.31550768772564</v>
+        <v>40.47555481453432</v>
       </c>
       <c r="D7" t="n">
-        <v>2.015671718279108</v>
+        <v>1.942590723913206</v>
       </c>
       <c r="E7" t="n">
-        <v>7.876565624686129</v>
+        <v>8.095525984462531</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478698179525405</v>
+        <v>0.7436770363346996</v>
       </c>
       <c r="G7" t="n">
-        <v>30.72791706512004</v>
+        <v>29.75837210803885</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40201162581685</v>
+        <v>34.20914367139618</v>
       </c>
       <c r="I7" t="n">
-        <v>3.189218055827437</v>
+        <v>3.993495831897617</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674186362203377</v>
+        <v>4.647981477091872</v>
       </c>
       <c r="K7" t="n">
-        <v>16.36655973011452</v>
+        <v>16.60921316686504</v>
       </c>
       <c r="L7" t="n">
-        <v>42.2117602702768</v>
+        <v>42.78232764582569</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89382768811696</v>
+        <v>99.86709562722504</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.64397792976929</v>
+        <v>81.30326281747179</v>
       </c>
       <c r="C8" t="n">
-        <v>43.66504627314828</v>
+        <v>39.00729403596078</v>
       </c>
       <c r="D8" t="n">
-        <v>2.0200107811699</v>
+        <v>1.843207044561817</v>
       </c>
       <c r="E8" t="n">
-        <v>9.746200151220409</v>
+        <v>8.236765802028698</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494797299956545</v>
+        <v>0.7446930980522933</v>
       </c>
       <c r="G8" t="n">
-        <v>31.24335176112272</v>
+        <v>28.23592248692309</v>
       </c>
       <c r="H8" t="n">
-        <v>34.4760675798001</v>
+        <v>34.25588251040549</v>
       </c>
       <c r="I8" t="n">
-        <v>5.724619613987662</v>
+        <v>3.332460012673554</v>
       </c>
       <c r="J8" t="n">
-        <v>4.68424831247284</v>
+        <v>4.654331862826833</v>
       </c>
       <c r="K8" t="n">
-        <v>11.3560220702307</v>
+        <v>18.69673718252821</v>
       </c>
       <c r="L8" t="n">
-        <v>44.78852089311777</v>
+        <v>42.18503834173607</v>
       </c>
       <c r="M8" t="n">
-        <v>99.80958923649676</v>
+        <v>99.88906956022507</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.87879681782168</v>
+        <v>79.17994965402838</v>
       </c>
       <c r="C9" t="n">
-        <v>42.78894736905936</v>
+        <v>37.40011693654936</v>
       </c>
       <c r="D9" t="n">
-        <v>1.940658366931722</v>
+        <v>1.743101746103267</v>
       </c>
       <c r="E9" t="n">
-        <v>10.15988257403021</v>
+        <v>8.25280722099134</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508540436445185</v>
+        <v>0.7455647288743392</v>
       </c>
       <c r="G9" t="n">
-        <v>30.01601405864676</v>
+        <v>26.70241844778359</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53928600764785</v>
+        <v>34.2959775282196</v>
       </c>
       <c r="I9" t="n">
-        <v>4.779263994142399</v>
+        <v>2.780300426591602</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69283777277824</v>
+        <v>4.65977955546462</v>
       </c>
       <c r="K9" t="n">
-        <v>13.12120318217831</v>
+        <v>20.82005034597163</v>
       </c>
       <c r="L9" t="n">
-        <v>43.93083223726266</v>
+        <v>41.68726438379362</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84098278850033</v>
+        <v>99.90743166631462</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.90886128784612</v>
+        <v>84.80827894485219</v>
       </c>
       <c r="C10" t="n">
-        <v>41.56126017913074</v>
+        <v>41.09060317460193</v>
       </c>
       <c r="D10" t="n">
-        <v>1.852784006802295</v>
+        <v>1.745223538961645</v>
       </c>
       <c r="E10" t="n">
-        <v>10.36466216700695</v>
+        <v>10.34651042706509</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520298629589789</v>
+        <v>0.746472268506332</v>
       </c>
       <c r="G10" t="n">
-        <v>28.65686807294208</v>
+        <v>28.30241453001004</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59337369611303</v>
+        <v>35.90521688007306</v>
       </c>
       <c r="I10" t="n">
-        <v>3.988956838529161</v>
+        <v>3.096989622071443</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700186643493617</v>
+        <v>4.665451678164574</v>
       </c>
       <c r="K10" t="n">
-        <v>15.0911387121539</v>
+        <v>15.19172105514782</v>
       </c>
       <c r="L10" t="n">
-        <v>43.21484377554475</v>
+        <v>43.61456829056106</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86724266682938</v>
+        <v>99.89689252031081</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.72329263819391</v>
+        <v>84.27355042278006</v>
       </c>
       <c r="C11" t="n">
-        <v>39.99479724318715</v>
+        <v>40.94860723857931</v>
       </c>
       <c r="D11" t="n">
-        <v>1.75606695920309</v>
+        <v>1.715053738628586</v>
       </c>
       <c r="E11" t="n">
-        <v>10.37838203359949</v>
+        <v>10.659397807241</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530385262599142</v>
+        <v>0.7472440403956836</v>
       </c>
       <c r="G11" t="n">
-        <v>27.16095291862337</v>
+        <v>27.86924809977253</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63977220795605</v>
+        <v>35.99843837760461</v>
       </c>
       <c r="I11" t="n">
-        <v>3.328589203427525</v>
+        <v>2.613893106664637</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706490789124463</v>
+        <v>4.670275252473022</v>
       </c>
       <c r="K11" t="n">
-        <v>17.2767073618061</v>
+        <v>15.72644957721993</v>
       </c>
       <c r="L11" t="n">
-        <v>42.61769103838095</v>
+        <v>43.23790340373262</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88919564337419</v>
+        <v>99.91296021953187</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.29866411987827</v>
+        <v>82.05238551182983</v>
       </c>
       <c r="C12" t="n">
-        <v>38.08611597540184</v>
+        <v>39.13281948434653</v>
       </c>
       <c r="D12" t="n">
-        <v>1.649612524834118</v>
+        <v>1.621830173681291</v>
       </c>
       <c r="E12" t="n">
-        <v>10.21207172682262</v>
+        <v>10.44335718253288</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539066206233844</v>
+        <v>0.7479058621647048</v>
       </c>
       <c r="G12" t="n">
-        <v>25.51443035026614</v>
+        <v>26.35438556121503</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67970454867568</v>
+        <v>36.03032160300504</v>
       </c>
       <c r="I12" t="n">
-        <v>2.777021969760176</v>
+        <v>2.18017349070147</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711916378896152</v>
+        <v>4.674411638529405</v>
       </c>
       <c r="K12" t="n">
-        <v>19.70133588012172</v>
+        <v>17.94761448817017</v>
       </c>
       <c r="L12" t="n">
-        <v>42.12008733327012</v>
+        <v>42.8469578856315</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90753918879368</v>
+        <v>99.9273918581482</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.84466499719575</v>
+        <v>83.32574173666907</v>
       </c>
       <c r="C13" t="n">
-        <v>36.06171959566376</v>
+        <v>40.16289684095617</v>
       </c>
       <c r="D13" t="n">
-        <v>1.542832967994682</v>
+        <v>1.623170113411292</v>
       </c>
       <c r="E13" t="n">
-        <v>9.937123547505175</v>
+        <v>11.12221283003429</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546544389287227</v>
+        <v>0.7485237744438554</v>
       </c>
       <c r="G13" t="n">
-        <v>23.86287913760423</v>
+        <v>26.70217230331127</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71410419072124</v>
+        <v>36.38610250585728</v>
       </c>
       <c r="I13" t="n">
-        <v>2.316480471137165</v>
+        <v>2.065286619336991</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716590243304517</v>
+        <v>4.678273590274096</v>
       </c>
       <c r="K13" t="n">
-        <v>22.15533500280426</v>
+        <v>16.67425826333093</v>
       </c>
       <c r="L13" t="n">
-        <v>41.70580590237198</v>
+        <v>43.09405883874807</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92286050083999</v>
+        <v>99.93121394303517</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.34352939913876</v>
+        <v>81.05911208953515</v>
       </c>
       <c r="C14" t="n">
-        <v>39.9238101826372</v>
+        <v>38.2162947378636</v>
       </c>
       <c r="D14" t="n">
-        <v>1.544809689958298</v>
+        <v>1.530987411267087</v>
       </c>
       <c r="E14" t="n">
-        <v>12.13562490493632</v>
+        <v>10.77761120868261</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556213238963868</v>
+        <v>0.7490539126023551</v>
       </c>
       <c r="G14" t="n">
-        <v>25.53890579748358</v>
+        <v>25.18570870180602</v>
       </c>
       <c r="H14" t="n">
-        <v>36.40403375217167</v>
+        <v>36.41187277800631</v>
       </c>
       <c r="I14" t="n">
-        <v>3.241900656340095</v>
+        <v>1.722291123406062</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722633274352417</v>
+        <v>4.681586953764719</v>
       </c>
       <c r="K14" t="n">
-        <v>15.65647060086122</v>
+        <v>18.94088791046484</v>
       </c>
       <c r="L14" t="n">
-        <v>44.31179413800426</v>
+        <v>42.7854482789122</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89207492150268</v>
+        <v>99.94263092724064</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.51518959115758</v>
+        <v>80.03560083794967</v>
       </c>
       <c r="C15" t="n">
-        <v>39.58994493207159</v>
+        <v>37.42798040508312</v>
       </c>
       <c r="D15" t="n">
-        <v>1.512993472236739</v>
+        <v>1.488629727450498</v>
       </c>
       <c r="E15" t="n">
-        <v>12.34338340075851</v>
+        <v>10.72379665983011</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564369750964361</v>
+        <v>0.7495113221910582</v>
       </c>
       <c r="G15" t="n">
-        <v>25.0198662279899</v>
+        <v>24.48889808270048</v>
       </c>
       <c r="H15" t="n">
-        <v>36.45027833087259</v>
+        <v>36.43410767922114</v>
       </c>
       <c r="I15" t="n">
-        <v>2.704500089850692</v>
+        <v>1.466211602862276</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727731094352725</v>
+        <v>4.684445763694113</v>
       </c>
       <c r="K15" t="n">
-        <v>16.48481040884242</v>
+        <v>19.96439916205031</v>
       </c>
       <c r="L15" t="n">
-        <v>43.83519186307653</v>
+        <v>42.55877653928284</v>
       </c>
       <c r="M15" t="n">
-        <v>99.90994720399054</v>
+        <v>99.95115610641628</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.96348986314152</v>
+        <v>77.42502570010996</v>
       </c>
       <c r="C16" t="n">
-        <v>37.45660536054479</v>
+        <v>35.04390115472994</v>
       </c>
       <c r="D16" t="n">
-        <v>1.414998867046229</v>
+        <v>1.383470843227149</v>
       </c>
       <c r="E16" t="n">
-        <v>11.91989250150116</v>
+        <v>10.17000035622898</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7571395153164043</v>
+        <v>0.7499057972084411</v>
       </c>
       <c r="G16" t="n">
-        <v>23.39936226817665</v>
+        <v>22.75896810028198</v>
       </c>
       <c r="H16" t="n">
-        <v>36.48413149696512</v>
+        <v>36.45328330050205</v>
       </c>
       <c r="I16" t="n">
-        <v>2.255843243408427</v>
+        <v>1.222486070108605</v>
       </c>
       <c r="J16" t="n">
-        <v>4.732121970727526</v>
+        <v>4.686911232552757</v>
       </c>
       <c r="K16" t="n">
-        <v>19.03651013685848</v>
+        <v>22.57497429989005</v>
       </c>
       <c r="L16" t="n">
-        <v>43.43175950010089</v>
+        <v>42.34039644530048</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92487499750416</v>
+        <v>99.95927189992047</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.56430803473228</v>
+        <v>82.88454431838053</v>
       </c>
       <c r="C17" t="n">
-        <v>38.60894806962081</v>
+        <v>38.57755439565155</v>
       </c>
       <c r="D17" t="n">
-        <v>1.416311198453052</v>
+        <v>1.384296653984348</v>
       </c>
       <c r="E17" t="n">
-        <v>12.68167753399726</v>
+        <v>12.05841174875659</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7578417193876841</v>
+        <v>0.7503534251994839</v>
       </c>
       <c r="G17" t="n">
-        <v>23.7889252331217</v>
+        <v>24.40751998427166</v>
       </c>
       <c r="H17" t="n">
-        <v>36.88582984520259</v>
+        <v>38.11000948961725</v>
       </c>
       <c r="I17" t="n">
-        <v>2.297211758396966</v>
+        <v>1.484244109054443</v>
       </c>
       <c r="J17" t="n">
-        <v>4.736510746173025</v>
+        <v>4.689708907496774</v>
       </c>
       <c r="K17" t="n">
-        <v>17.43569196526771</v>
+        <v>17.11545568161945</v>
       </c>
       <c r="L17" t="n">
-        <v>43.87885719182626</v>
+        <v>44.25754463359492</v>
       </c>
       <c r="M17" t="n">
-        <v>99.9234972267148</v>
+        <v>99.95055471086592</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.16514244752506</v>
+        <v>84.52779362574887</v>
       </c>
       <c r="C18" t="n">
-        <v>36.5646472864187</v>
+        <v>39.36037969543769</v>
       </c>
       <c r="D18" t="n">
-        <v>1.327680994382185</v>
+        <v>1.385548602277911</v>
       </c>
       <c r="E18" t="n">
-        <v>12.20739235363667</v>
+        <v>12.70371790272739</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7584454418112535</v>
+        <v>0.7510320396334235</v>
       </c>
       <c r="G18" t="n">
-        <v>22.30025713507864</v>
+        <v>24.55567840522553</v>
       </c>
       <c r="H18" t="n">
-        <v>36.91521434861514</v>
+        <v>38.14447591790116</v>
       </c>
       <c r="I18" t="n">
-        <v>1.915868162680827</v>
+        <v>2.293390510274553</v>
       </c>
       <c r="J18" t="n">
-        <v>4.740284011320334</v>
+        <v>4.693950247708896</v>
       </c>
       <c r="K18" t="n">
-        <v>19.83485755247495</v>
+        <v>15.47220637425114</v>
       </c>
       <c r="L18" t="n">
-        <v>43.53668372337309</v>
+        <v>45.09103665504673</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93618856226674</v>
+        <v>99.92362272473557</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.18117599346665</v>
+        <v>81.53466085999528</v>
       </c>
       <c r="C19" t="n">
-        <v>35.87590227122269</v>
+        <v>36.72137064387102</v>
       </c>
       <c r="D19" t="n">
-        <v>1.292093962406644</v>
+        <v>1.279234432203338</v>
       </c>
       <c r="E19" t="n">
-        <v>12.1464583633654</v>
+        <v>12.04772775049221</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7589555443795174</v>
+        <v>0.7516193006397124</v>
       </c>
       <c r="G19" t="n">
-        <v>21.70252321624816</v>
+        <v>22.67150302084877</v>
       </c>
       <c r="H19" t="n">
-        <v>36.94004216695138</v>
+        <v>38.17430255928232</v>
       </c>
       <c r="I19" t="n">
-        <v>1.597630587743569</v>
+        <v>1.912653167530723</v>
       </c>
       <c r="J19" t="n">
-        <v>4.743472152371983</v>
+        <v>4.697620628998202</v>
       </c>
       <c r="K19" t="n">
-        <v>20.81882400653335</v>
+        <v>18.46533914000473</v>
       </c>
       <c r="L19" t="n">
-        <v>43.25205516216949</v>
+        <v>44.74958492417219</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94678143992552</v>
+        <v>99.93629470804794</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.57694294579633</v>
+        <v>78.425554237939</v>
       </c>
       <c r="C20" t="n">
-        <v>33.51769117591603</v>
+        <v>33.90662415539592</v>
       </c>
       <c r="D20" t="n">
-        <v>1.197033244984051</v>
+        <v>1.169542130483743</v>
       </c>
       <c r="E20" t="n">
-        <v>11.47485239889507</v>
+        <v>11.28048076742126</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7593956368505522</v>
+        <v>0.7521288290004181</v>
       </c>
       <c r="G20" t="n">
-        <v>20.10584566272535</v>
+        <v>20.72745798328966</v>
       </c>
       <c r="H20" t="n">
-        <v>36.96146243926874</v>
+        <v>38.20018120527713</v>
       </c>
       <c r="I20" t="n">
-        <v>1.332130832756622</v>
+        <v>1.594958141214182</v>
       </c>
       <c r="J20" t="n">
-        <v>4.746222730315951</v>
+        <v>4.700805181252612</v>
       </c>
       <c r="K20" t="n">
-        <v>23.42305705420366</v>
+        <v>21.574445762061</v>
       </c>
       <c r="L20" t="n">
-        <v>43.01487314244301</v>
+        <v>44.46580082788946</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95562137256269</v>
+        <v>99.94687074534639</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.5194225296941</v>
+        <v>75.36562335838846</v>
       </c>
       <c r="C21" t="n">
-        <v>37.05584315924338</v>
+        <v>31.09120079470205</v>
       </c>
       <c r="D21" t="n">
-        <v>1.198050315778372</v>
+        <v>1.062300736751099</v>
       </c>
       <c r="E21" t="n">
-        <v>13.42073863077914</v>
+        <v>10.4677671480253</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7600408646475345</v>
+        <v>0.752571235101938</v>
       </c>
       <c r="G21" t="n">
-        <v>21.70849820110664</v>
+        <v>18.82684968135238</v>
       </c>
       <c r="H21" t="n">
-        <v>38.57843651434547</v>
+        <v>38.22265075117506</v>
       </c>
       <c r="I21" t="n">
-        <v>2.103402598989839</v>
+        <v>1.329913586595572</v>
       </c>
       <c r="J21" t="n">
-        <v>4.75025540404709</v>
+        <v>4.703570219387112</v>
       </c>
       <c r="K21" t="n">
-        <v>17.48057747030588</v>
+        <v>24.63437664161154</v>
       </c>
       <c r="L21" t="n">
-        <v>45.39352547245172</v>
+        <v>44.23011817087489</v>
       </c>
       <c r="M21" t="n">
-        <v>99.929946102001</v>
+        <v>99.95569560718847</v>
       </c>
     </row>
   </sheetData>
